--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.06862</v>
+        <v>17.39195</v>
       </c>
       <c r="D2" t="n">
-        <v>17.42521</v>
+        <v>17.19963</v>
       </c>
       <c r="E2" t="n">
-        <v>17.22892</v>
+        <v>17.21299</v>
       </c>
       <c r="F2" t="n">
-        <v>42.45222</v>
+        <v>44.32664</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05127</v>
+        <v>0.05216</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8892</v>
+        <v>1.89485</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.35823</v>
+        <v>17.15206</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53342</v>
+        <v>16.89343</v>
       </c>
       <c r="E3" t="n">
-        <v>17.26167</v>
+        <v>17.05316</v>
       </c>
       <c r="F3" t="n">
-        <v>43.36379</v>
+        <v>44.18946</v>
       </c>
       <c r="G3" t="n">
-        <v>0.052</v>
+        <v>0.05258</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84633</v>
+        <v>1.9165</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.30463</v>
+        <v>17.17721</v>
       </c>
       <c r="D4" t="n">
-        <v>17.46993</v>
+        <v>16.81989</v>
       </c>
       <c r="E4" t="n">
-        <v>17.09382</v>
+        <v>17.09195</v>
       </c>
       <c r="F4" t="n">
-        <v>43.42757</v>
+        <v>43.17317</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0516</v>
+        <v>0.05254</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86948</v>
+        <v>1.85671</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.95666</v>
+        <v>17.228</v>
       </c>
       <c r="D6" t="n">
-        <v>16.55766</v>
+        <v>16.58743</v>
       </c>
       <c r="E6" t="n">
-        <v>16.85454</v>
+        <v>17.06528</v>
       </c>
       <c r="F6" t="n">
-        <v>22.95556</v>
+        <v>22.58125</v>
       </c>
       <c r="G6" t="n">
-        <v>35.24012</v>
+        <v>35.4941</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.86754</v>
+        <v>17.14689</v>
       </c>
       <c r="D7" t="n">
-        <v>16.43992</v>
+        <v>16.46112</v>
       </c>
       <c r="E7" t="n">
-        <v>16.81171</v>
+        <v>16.49869</v>
       </c>
       <c r="F7" t="n">
-        <v>22.28987</v>
+        <v>22.66539</v>
       </c>
       <c r="G7" t="n">
-        <v>35.53417</v>
+        <v>34.48986</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.31044</v>
+        <v>17.12001</v>
       </c>
       <c r="D8" t="n">
-        <v>16.43409</v>
+        <v>16.5796</v>
       </c>
       <c r="E8" t="n">
-        <v>16.95489</v>
+        <v>16.92656</v>
       </c>
       <c r="F8" t="n">
-        <v>22.34425</v>
+        <v>22.64313</v>
       </c>
       <c r="G8" t="n">
-        <v>34.7003</v>
+        <v>35.03113</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.62407</v>
+        <v>0.62726</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14995</v>
+        <v>1.12687</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.63087</v>
+        <v>0.62119</v>
       </c>
       <c r="D11" t="n">
-        <v>1.14764</v>
+        <v>1.15697</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.62078</v>
+        <v>0.6231</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13536</v>
+        <v>1.16867</v>
       </c>
     </row>
   </sheetData>
